--- a/Python/dz2/work/output/animals_attention_list.xlsx
+++ b/Python/dz2/work/output/animals_attention_list.xlsx
@@ -651,7 +651,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K2" t="s">
         <v>70</v>
@@ -686,7 +686,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K3" t="s">
         <v>71</v>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K4" t="s">
         <v>71</v>
@@ -753,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K5" t="s">
         <v>70</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s">
         <v>70</v>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K7" t="s">
         <v>70</v>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
         <v>70</v>
@@ -890,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
         <v>71</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
         <v>71</v>
@@ -957,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
         <v>70</v>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K12" t="s">
         <v>71</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s">
         <v>71</v>
@@ -1062,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K14" t="s">
         <v>70</v>
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K15" t="s">
         <v>70</v>
@@ -1129,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="J16">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K16" t="s">
         <v>71</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K17" t="s">
         <v>71</v>
@@ -1199,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K18" t="s">
         <v>70</v>
@@ -1231,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K19" t="s">
         <v>70</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K20" t="s">
         <v>71</v>
@@ -1298,7 +1298,7 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K21" t="s">
         <v>70</v>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" t="s">
         <v>71</v>
@@ -1368,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K23" t="s">
         <v>71</v>
